--- a/manu_sourcedata/extended_data_fig8.xlsx
+++ b/manu_sourcedata/extended_data_fig8.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyj/Doc/1_dod_dec25/manu_sourcedata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3E9AB8-4B61-FC43-8E96-6313D41D9EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CA0C15-6F7D-B442-B94A-5F59AE406711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{ED1ECD1F-5193-4245-9D87-00687259A86C}"/>
+    <workbookView xWindow="10080" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{ED1ECD1F-5193-4245-9D87-00687259A86C}"/>
   </bookViews>
   <sheets>
-    <sheet name="7a" sheetId="1" r:id="rId1"/>
+    <sheet name="8a" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/manu_sourcedata/extended_data_fig8.xlsx
+++ b/manu_sourcedata/extended_data_fig8.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yyj/Doc/1_dod_dec25/manu_sourcedata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CA0C15-6F7D-B442-B94A-5F59AE406711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B55CC8B-AFCE-294E-8B39-EB61908A38B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{ED1ECD1F-5193-4245-9D87-00687259A86C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{ED1ECD1F-5193-4245-9D87-00687259A86C}"/>
   </bookViews>
   <sheets>
     <sheet name="8a" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="35">
   <si>
     <t>sample</t>
   </si>
@@ -2927,4 +2928,371 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A99E9E-CB50-7144-820F-8122BB098D90}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>2.02593192868719E-3</v>
+      </c>
+      <c r="D2">
+        <v>22212</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>4.3551899346721502E-3</v>
+      </c>
+      <c r="D3">
+        <v>4133</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>9.4151358542700694E-3</v>
+      </c>
+      <c r="D4">
+        <v>39086</v>
+      </c>
+      <c r="E4">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>2.8144165336469701E-3</v>
+      </c>
+      <c r="D5">
+        <v>47612</v>
+      </c>
+      <c r="E5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>9.5686435040679505E-3</v>
+      </c>
+      <c r="D6">
+        <v>39086</v>
+      </c>
+      <c r="E6">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>9.5144081324035901E-3</v>
+      </c>
+      <c r="D7">
+        <v>47612</v>
+      </c>
+      <c r="E7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>9.6198127206672396E-3</v>
+      </c>
+      <c r="D8">
+        <v>39086</v>
+      </c>
+      <c r="E8">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>4.8727211627320804E-3</v>
+      </c>
+      <c r="D9">
+        <v>47612</v>
+      </c>
+      <c r="E9">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>2.2770301386685701E-2</v>
+      </c>
+      <c r="D10">
+        <v>39086</v>
+      </c>
+      <c r="E10">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>2.33134503906578E-3</v>
+      </c>
+      <c r="D11">
+        <v>47612</v>
+      </c>
+      <c r="E11">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>2.35378396356751E-3</v>
+      </c>
+      <c r="D12">
+        <v>39086</v>
+      </c>
+      <c r="E12">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13">
+        <v>1.11106443753675E-2</v>
+      </c>
+      <c r="D13">
+        <v>47612</v>
+      </c>
+      <c r="E13">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>2.3614593460574099E-2</v>
+      </c>
+      <c r="D14">
+        <v>39086</v>
+      </c>
+      <c r="E14">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>5.3983523512255004E-3</v>
+      </c>
+      <c r="D15">
+        <v>39086</v>
+      </c>
+      <c r="E15">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>8.1870746558870095E-4</v>
+      </c>
+      <c r="D16">
+        <v>39086</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17">
+        <v>3.5818451619505702E-4</v>
+      </c>
+      <c r="D17">
+        <v>39086</v>
+      </c>
+      <c r="E17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>4.00109216163992E-2</v>
+      </c>
+      <c r="D18">
+        <v>47612</v>
+      </c>
+      <c r="E18">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>1.7033520961102201E-2</v>
+      </c>
+      <c r="D19">
+        <v>47612</v>
+      </c>
+      <c r="E19">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20">
+        <v>4.2006216920104098E-3</v>
+      </c>
+      <c r="D20">
+        <v>47612</v>
+      </c>
+      <c r="E20">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>3.5915315466689001E-3</v>
+      </c>
+      <c r="D21">
+        <v>47612</v>
+      </c>
+      <c r="E21">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>